--- a/resources/templates/standard/B1100-04.xlsx
+++ b/resources/templates/standard/B1100-04.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>수리 / 재작업 작업 일지</t>
   </si>
@@ -800,10 +803,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -814,18 +819,18 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P1" s="4"/>
       <c r="Q1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R1" s="4"/>
     </row>
@@ -871,7 +876,7 @@
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -893,42 +898,42 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
       <c r="N5" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
@@ -943,23 +948,23 @@
       <c r="G6" s="12"/>
       <c r="H6" s="11"/>
       <c r="I6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="16"/>
       <c r="N6" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P6" s="12"/>
       <c r="Q6" s="12"/>
